--- a/artfynd/A 8446-2025 artfynd.xlsx
+++ b/artfynd/A 8446-2025 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122880589</v>
+        <v>122880590</v>
       </c>
       <c r="B3" t="n">
         <v>100621</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574320</v>
+        <v>574318</v>
       </c>
       <c r="R3" t="n">
-        <v>6699041</v>
+        <v>6699037</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122880590</v>
+        <v>122880589</v>
       </c>
       <c r="B4" t="n">
         <v>100621</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574318</v>
+        <v>574320</v>
       </c>
       <c r="R4" t="n">
-        <v>6699037</v>
+        <v>6699041</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 8446-2025 artfynd.xlsx
+++ b/artfynd/A 8446-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122880585</v>
+        <v>122880590</v>
       </c>
       <c r="B2" t="n">
-        <v>91235</v>
+        <v>100623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574289</v>
+        <v>574318</v>
       </c>
       <c r="R2" t="n">
-        <v>6699126</v>
+        <v>6699037</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122880590</v>
+        <v>122880589</v>
       </c>
       <c r="B3" t="n">
-        <v>100621</v>
+        <v>100623</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574318</v>
+        <v>574320</v>
       </c>
       <c r="R3" t="n">
-        <v>6699037</v>
+        <v>6699041</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122880589</v>
+        <v>122880585</v>
       </c>
       <c r="B4" t="n">
-        <v>100621</v>
+        <v>91235</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574320</v>
+        <v>574289</v>
       </c>
       <c r="R4" t="n">
-        <v>6699041</v>
+        <v>6699126</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 8446-2025 artfynd.xlsx
+++ b/artfynd/A 8446-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122880590</v>
+        <v>122880585</v>
       </c>
       <c r="B2" t="n">
-        <v>100623</v>
+        <v>91235</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574318</v>
+        <v>574289</v>
       </c>
       <c r="R2" t="n">
-        <v>6699037</v>
+        <v>6699126</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122880589</v>
+        <v>122880590</v>
       </c>
       <c r="B3" t="n">
         <v>100623</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574320</v>
+        <v>574318</v>
       </c>
       <c r="R3" t="n">
-        <v>6699041</v>
+        <v>6699037</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122880585</v>
+        <v>122880589</v>
       </c>
       <c r="B4" t="n">
-        <v>91235</v>
+        <v>100623</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574289</v>
+        <v>574320</v>
       </c>
       <c r="R4" t="n">
-        <v>6699126</v>
+        <v>6699041</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 8446-2025 artfynd.xlsx
+++ b/artfynd/A 8446-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122880585</v>
+        <v>122880590</v>
       </c>
       <c r="B2" t="n">
-        <v>91235</v>
+        <v>100631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574289</v>
+        <v>574318</v>
       </c>
       <c r="R2" t="n">
-        <v>6699126</v>
+        <v>6699037</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122880590</v>
+        <v>122880589</v>
       </c>
       <c r="B3" t="n">
-        <v>100623</v>
+        <v>100631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574318</v>
+        <v>574320</v>
       </c>
       <c r="R3" t="n">
-        <v>6699037</v>
+        <v>6699041</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122880589</v>
+        <v>122880585</v>
       </c>
       <c r="B4" t="n">
-        <v>100623</v>
+        <v>91243</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574320</v>
+        <v>574289</v>
       </c>
       <c r="R4" t="n">
-        <v>6699041</v>
+        <v>6699126</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 8446-2025 artfynd.xlsx
+++ b/artfynd/A 8446-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122880590</v>
+        <v>122880589</v>
       </c>
       <c r="B2" t="n">
         <v>100631</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574318</v>
+        <v>574320</v>
       </c>
       <c r="R2" t="n">
-        <v>6699037</v>
+        <v>6699041</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122880589</v>
+        <v>122880585</v>
       </c>
       <c r="B3" t="n">
-        <v>100631</v>
+        <v>91243</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574320</v>
+        <v>574289</v>
       </c>
       <c r="R3" t="n">
-        <v>6699041</v>
+        <v>6699126</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122880585</v>
+        <v>122880590</v>
       </c>
       <c r="B4" t="n">
-        <v>91243</v>
+        <v>100631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574289</v>
+        <v>574318</v>
       </c>
       <c r="R4" t="n">
-        <v>6699126</v>
+        <v>6699037</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 8446-2025 artfynd.xlsx
+++ b/artfynd/A 8446-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122880585</v>
+        <v>122880590</v>
       </c>
       <c r="B3" t="n">
-        <v>91243</v>
+        <v>100631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574289</v>
+        <v>574318</v>
       </c>
       <c r="R3" t="n">
-        <v>6699126</v>
+        <v>6699037</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122880590</v>
+        <v>122880585</v>
       </c>
       <c r="B4" t="n">
-        <v>100631</v>
+        <v>91243</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574318</v>
+        <v>574289</v>
       </c>
       <c r="R4" t="n">
-        <v>6699037</v>
+        <v>6699126</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 8446-2025 artfynd.xlsx
+++ b/artfynd/A 8446-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122880589</v>
+        <v>122880590</v>
       </c>
       <c r="B2" t="n">
         <v>100631</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574320</v>
+        <v>574318</v>
       </c>
       <c r="R2" t="n">
-        <v>6699041</v>
+        <v>6699037</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122880590</v>
+        <v>122880589</v>
       </c>
       <c r="B3" t="n">
         <v>100631</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574318</v>
+        <v>574320</v>
       </c>
       <c r="R3" t="n">
-        <v>6699037</v>
+        <v>6699041</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 8446-2025 artfynd.xlsx
+++ b/artfynd/A 8446-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122880590</v>
+        <v>122880585</v>
       </c>
       <c r="B2" t="n">
-        <v>100631</v>
+        <v>91242</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574318</v>
+        <v>574289</v>
       </c>
       <c r="R2" t="n">
-        <v>6699037</v>
+        <v>6699126</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,7 +780,7 @@
         <v>122880589</v>
       </c>
       <c r="B3" t="n">
-        <v>100631</v>
+        <v>100634</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122880585</v>
+        <v>122880590</v>
       </c>
       <c r="B4" t="n">
-        <v>91243</v>
+        <v>100634</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574289</v>
+        <v>574318</v>
       </c>
       <c r="R4" t="n">
-        <v>6699126</v>
+        <v>6699037</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 8446-2025 artfynd.xlsx
+++ b/artfynd/A 8446-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122880585</v>
+        <v>122880590</v>
       </c>
       <c r="B2" t="n">
-        <v>91242</v>
+        <v>100636</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574289</v>
+        <v>574318</v>
       </c>
       <c r="R2" t="n">
-        <v>6699126</v>
+        <v>6699037</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,7 +780,7 @@
         <v>122880589</v>
       </c>
       <c r="B3" t="n">
-        <v>100634</v>
+        <v>100636</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122880590</v>
+        <v>122880585</v>
       </c>
       <c r="B4" t="n">
-        <v>100634</v>
+        <v>91244</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574318</v>
+        <v>574289</v>
       </c>
       <c r="R4" t="n">
-        <v>6699037</v>
+        <v>6699126</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 8446-2025 artfynd.xlsx
+++ b/artfynd/A 8446-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122880590</v>
       </c>
       <c r="B2" t="n">
-        <v>100636</v>
+        <v>100642</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>122880589</v>
       </c>
       <c r="B3" t="n">
-        <v>100636</v>
+        <v>100642</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>122880585</v>
       </c>
       <c r="B4" t="n">
-        <v>91244</v>
+        <v>91250</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
